--- a/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
+++ b/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-india\InputData\web-app\OCCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\web-app\OCCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA9F84F-F18F-4E0A-B715-EF9283B2163A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6FEF58-08A4-48D5-A6A7-14155C535D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>Source:</t>
   </si>
@@ -60,6 +60,15 @@
     <t>web application interface do not get too large.</t>
   </si>
   <si>
+    <t>Dollars</t>
+  </si>
+  <si>
+    <t>One Large Output Currency Unit</t>
+  </si>
+  <si>
+    <t>For the U.S. model:</t>
+  </si>
+  <si>
     <t>Large Output Currency Unit</t>
   </si>
   <si>
@@ -75,84 +84,50 @@
     <t>OCCF Dollars per Small Output Currency Unit</t>
   </si>
   <si>
+    <t>See cpi.xlsx</t>
+  </si>
+  <si>
+    <t>value less than 1 in this variable.</t>
+  </si>
+  <si>
+    <t>This is why we multiply, not divide, by the conversion</t>
+  </si>
+  <si>
+    <t>factor above.</t>
+  </si>
+  <si>
     <t>Medium Output Currency Unit</t>
   </si>
   <si>
     <t>OCCF Dollars per Medium Output Currency Unit</t>
   </si>
   <si>
-    <t>See scaling-factors.xlsx</t>
-  </si>
-  <si>
-    <t>For the India model:</t>
-  </si>
-  <si>
-    <t>2018 lakhs</t>
-  </si>
-  <si>
-    <t>rupees per lakh</t>
-  </si>
-  <si>
-    <t>2018 rupees</t>
-  </si>
-  <si>
-    <t>Ruppees per dollar</t>
-  </si>
-  <si>
-    <t>Rupees</t>
-  </si>
-  <si>
-    <t>Crores</t>
-  </si>
-  <si>
-    <t>Lakhs</t>
-  </si>
-  <si>
-    <t>https://www.poundsterlinglive.com/best-exchange-rates/best-us-dollar-to-indian-rupee-history-2018</t>
-  </si>
-  <si>
-    <t>US Inflation Rate</t>
-  </si>
-  <si>
-    <t>see cpi.xlsx</t>
-  </si>
-  <si>
     <t>Recall, this variable is "dollars per large/medium/small currency output unit"</t>
   </si>
   <si>
-    <t>2012 dollars are worth more than 2018 dollars, so we need a</t>
-  </si>
-  <si>
-    <t>value less than 1 in this variable.</t>
-  </si>
-  <si>
-    <t>This is why we multiply, not divide, by the conversion</t>
-  </si>
-  <si>
-    <t>factor above.</t>
-  </si>
-  <si>
-    <t>which in this case is "2012 dollars per 2018 rupee."</t>
-  </si>
-  <si>
-    <t>2018 to 2012 dollar adjustment</t>
-  </si>
-  <si>
-    <t>2018 lakh crores</t>
-  </si>
-  <si>
-    <t>rupees per lakh crore</t>
+    <t>2012 dollars are worth more than 2020 dollars, so we need a</t>
+  </si>
+  <si>
+    <t>2023 dollars per 2012 dollar</t>
+  </si>
+  <si>
+    <t>billion 2023 dollars</t>
+  </si>
+  <si>
+    <t>million 2023 dollars</t>
+  </si>
+  <si>
+    <t>2023 dollars</t>
+  </si>
+  <si>
+    <t>which in this case is "2012 dollars per 2023 dollar."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0E+00"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,14 +137,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -203,29 +170,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -244,9 +198,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -284,9 +238,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -319,26 +273,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -371,26 +308,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -564,26 +484,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
     <col min="2" max="2" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -591,7 +510,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -605,7 +524,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
@@ -631,147 +550,79 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="9">
-        <f>10^7*10^5</f>
-        <v>1000000000000</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="6"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>0.75350342301658668</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <f>10^5</f>
-        <v>100000</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="6"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>2018</v>
-      </c>
-      <c r="B29">
-        <v>68.492000000000004</v>
-      </c>
-      <c r="C29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="10">
-        <v>0.9143273584567535</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="11"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B40" s="13"/>
-      <c r="C40" s="12"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -791,17 +642,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B1" s="4" t="s">
-        <v>22</v>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3">
-        <f>About!A19/About!B29*About!B32</f>
-        <v>13349403703.450817</v>
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
+        <f>10^9*About!$A$26</f>
+        <v>753503423.01658666</v>
       </c>
     </row>
   </sheetData>
@@ -821,17 +672,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B1" s="4" t="s">
-        <v>23</v>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="8">
-        <f>About!A23/About!B29*About!B32</f>
-        <v>1334.9403703450819</v>
+        <v>8</v>
+      </c>
+      <c r="B2" s="6">
+        <f>10^6*About!$A$26</f>
+        <v>753503.42301658669</v>
       </c>
     </row>
   </sheetData>
@@ -851,17 +702,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B1" s="4" t="s">
-        <v>10</v>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="7">
-        <f>1/About!B29*About!B32</f>
-        <v>1.3349403703450818E-2</v>
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <f>1*About!A26</f>
+        <v>0.75350342301658668</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
+++ b/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29103"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\web-app\OCCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6FEF58-08A4-48D5-A6A7-14155C535D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{6B6FEF58-08A4-48D5-A6A7-14155C535D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02B8CEDD-50B2-48D4-A13E-89C1854AF0EE}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="OCCF-DpMOCU" sheetId="4" r:id="rId3"/>
     <sheet name="OCCF-DpSOCU" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,11 +39,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+  <si>
+    <t>OCCF Dollars per Large Output Currency Unit</t>
+  </si>
+  <si>
+    <t>OCCF Dollars per Medium Output Currency Unit</t>
+  </si>
+  <si>
+    <t>OCCF Dollars per Small Output Currency Unit</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>See cpi.xlsx</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -60,31 +77,58 @@
     <t>web application interface do not get too large.</t>
   </si>
   <si>
-    <t>Dollars</t>
-  </si>
-  <si>
-    <t>One Large Output Currency Unit</t>
-  </si>
-  <si>
-    <t>For the U.S. model:</t>
+    <t>For the India model:</t>
   </si>
   <si>
     <t>Large Output Currency Unit</t>
   </si>
   <si>
+    <t>2021 lakh crores</t>
+  </si>
+  <si>
+    <t>rupees per lakh crore</t>
+  </si>
+  <si>
+    <t>Medium Output Currency Unit</t>
+  </si>
+  <si>
+    <t>2021 lakhs</t>
+  </si>
+  <si>
+    <t>rupees per lakh</t>
+  </si>
+  <si>
     <t>Small Output Currency Unit</t>
   </si>
   <si>
-    <t>One Small Output Currency Unit</t>
-  </si>
-  <si>
-    <t>OCCF Dollars per Large Output Currency Unit</t>
-  </si>
-  <si>
-    <t>OCCF Dollars per Small Output Currency Unit</t>
-  </si>
-  <si>
-    <t>See cpi.xlsx</t>
+    <t>2021 rupees</t>
+  </si>
+  <si>
+    <t>Rupees per dollar</t>
+  </si>
+  <si>
+    <t>https://www.poundsterlinglive.com/history/USD-INR-2021</t>
+  </si>
+  <si>
+    <t>US Inflation Rate</t>
+  </si>
+  <si>
+    <t>see cpi.xlsx</t>
+  </si>
+  <si>
+    <t>2021 to 2012 dollar adjustment</t>
+  </si>
+  <si>
+    <t>2021 rupees per 2012 dollar</t>
+  </si>
+  <si>
+    <t>Recall, this variable is "dollars per large/medium/small currency output unit"</t>
+  </si>
+  <si>
+    <t>which in this case is "2012 dollars per 2021 rupee"</t>
+  </si>
+  <si>
+    <t>2012 dollars are worth more than 2018 rupees, so we need a</t>
   </si>
   <si>
     <t>value less than 1 in this variable.</t>
@@ -96,38 +140,27 @@
     <t>factor above.</t>
   </si>
   <si>
-    <t>Medium Output Currency Unit</t>
-  </si>
-  <si>
-    <t>OCCF Dollars per Medium Output Currency Unit</t>
-  </si>
-  <si>
-    <t>Recall, this variable is "dollars per large/medium/small currency output unit"</t>
-  </si>
-  <si>
-    <t>2012 dollars are worth more than 2020 dollars, so we need a</t>
-  </si>
-  <si>
-    <t>2023 dollars per 2012 dollar</t>
-  </si>
-  <si>
-    <t>billion 2023 dollars</t>
-  </si>
-  <si>
-    <t>million 2023 dollars</t>
-  </si>
-  <si>
-    <t>2023 dollars</t>
-  </si>
-  <si>
-    <t>which in this case is "2012 dollars per 2023 dollar."</t>
+    <t>2021 Lakh Crore Rupees</t>
+  </si>
+  <si>
+    <t>2012 Dollars</t>
+  </si>
+  <si>
+    <t>2018 Lakh Rupees</t>
+  </si>
+  <si>
+    <t>2018 Rupees</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0E+00"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,6 +170,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -167,10 +216,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -180,8 +230,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -484,149 +546,218 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15"/>
+    <row r="17" spans="1:3" ht="15">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:3" ht="15">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="19" spans="1:3" ht="15">
+      <c r="A19" s="7">
+        <f>10^7*10^5</f>
+        <v>1000000000000</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21" spans="1:3" ht="15">
+      <c r="A21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:3" ht="15">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15">
+      <c r="A23">
+        <f>10^5</f>
+        <v>100000</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15"/>
+    <row r="25" spans="1:3" ht="15">
+      <c r="A25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="1:3" ht="15">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15"/>
+    <row r="28" spans="1:3" ht="15">
+      <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="29" spans="1:3" ht="15">
+      <c r="A29">
+        <v>2021</v>
+      </c>
+      <c r="B29">
+        <v>73.946299999999994</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15"/>
+    <row r="31" spans="1:3" ht="15">
+      <c r="A31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30.75">
+      <c r="A32" s="9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B32" s="10">
+        <v>0.84699999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15">
+      <c r="B33" s="11"/>
+      <c r="C33" s="12"/>
+    </row>
+    <row r="34" spans="1:3" ht="15"/>
+    <row r="35" spans="1:3" ht="15">
+      <c r="A35">
+        <f xml:space="preserve"> B32/B29</f>
+        <v>1.1454258022375697E-2</v>
+      </c>
+      <c r="B35" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+    <row r="36" spans="1:3" ht="15"/>
+    <row r="37" spans="1:3" ht="15">
+      <c r="B37" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>0.75350342301658668</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
+    <row r="38" spans="1:3" ht="15">
+      <c r="B38" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
-        <v>19</v>
-      </c>
-    </row>
+    <row r="39" spans="1:3" ht="15">
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15">
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15">
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15">
+      <c r="B42" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C29" r:id="rId1" xr:uid="{4871607C-F158-41DE-AFBD-654EC8BE9EA1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -636,23 +767,24 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="B1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2">
-        <f>10^9*About!$A$26</f>
-        <v>753503423.01658666</v>
+        <f>About!A19*About!A35</f>
+        <v>11454258022.375696</v>
       </c>
     </row>
   </sheetData>
@@ -666,23 +798,24 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B2" s="6">
-        <f>10^6*About!$A$26</f>
-        <v>753503.42301658669</v>
+        <f>About!A23*About!A35</f>
+        <v>1145.4258022375698</v>
       </c>
     </row>
   </sheetData>
@@ -696,26 +829,198 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B2">
-        <f>1*About!A26</f>
-        <v>0.75350342301658668</v>
+        <f>1*About!A35</f>
+        <v>1.1454258022375697E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D89D9831-0D8F-445C-97B1-06DD8D5A26BB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70C4FDE8-77B3-496C-8EFF-F2C7F3165FDA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D49C68DE-7E7C-4AD9-ACC2-1533DF0251E4}"/>
 </file>